--- a/sample-files/sample_warning_june_2025.xlsx
+++ b/sample-files/sample_warning_june_2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/divesh/Desktop/sample-files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/divesh/Desktop/imd copy/sample-files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1F6DDB-93F6-5649-A8D1-833859B0F544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4EA227-6671-BC4A-99B5-5FFB5483BBA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15600" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Day1" sheetId="1" r:id="rId1"/>
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -3346,7 +3346,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AE29" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AE3 A5:AE29 A4:K4 M4:AE4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3676,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -6536,7 +6536,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -9396,7 +9396,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -9426,7 +9426,7 @@
         <v>0</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -12256,10 +12256,10 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>0</v>
